--- a/app/content/jieyu.xlsx
+++ b/app/content/jieyu.xlsx
@@ -1135,7 +1135,7 @@
         <v>固守反击</v>
       </c>
       <c r="C2" t="str">
-        <v>理</v>
+        <v>器</v>
       </c>
       <c r="D2" t="str">
         <v>依城而守，以火器迎敌。</v>
@@ -1158,7 +1158,7 @@
         <v>开门逆击</v>
       </c>
       <c r="C3" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D3" t="str">
         <v>背城死战，不留退路。</v>
@@ -1181,7 +1181,7 @@
         <v>驰援侧翼</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D4" t="str">
         <v>分兵救友军之急。</v>
@@ -1204,7 +1204,7 @@
         <v>民助城防</v>
       </c>
       <c r="C5" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D5" t="str">
         <v>发动百姓运砖送料。</v>
@@ -1227,7 +1227,7 @@
         <v>纵马疾驰</v>
       </c>
       <c r="C6" t="str">
-        <v>威</v>
+        <v>隐</v>
       </c>
       <c r="D6" t="str">
         <v>不恋战，只突围。</v>
@@ -1250,7 +1250,7 @@
         <v>避其锋芒</v>
       </c>
       <c r="C7" t="str">
-        <v>理</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>绕路、潜行、藏锋。</v>
@@ -1273,7 +1273,7 @@
         <v>留人一命</v>
       </c>
       <c r="C8" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D8" t="str">
         <v>刀下留人，饶敌伤兵。</v>
@@ -1296,7 +1296,7 @@
         <v>乾纲独断</v>
       </c>
       <c r="C9" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D9" t="str">
         <v>「朕意已决，不必再议！」</v>
@@ -1319,7 +1319,7 @@
         <v>垂询旧臣</v>
       </c>
       <c r="C10" t="str">
-        <v>理</v>
+        <v>隐</v>
       </c>
       <c r="D10" t="str">
         <v>先问太后，再问百官，再等一等。</v>
@@ -1342,7 +1342,7 @@
         <v>推诚相待</v>
       </c>
       <c r="C11" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D11" t="str">
         <v>把心里的怕，说给信得过的人。</v>
@@ -1506,7 +1506,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>理,威,利,理,威,情,利</v>
+        <v>策,势,策,策,势,策,策</v>
       </c>
       <c r="I4" t="str">
         <v>j_jue,j_nai,j_ren,j_yuan</v>
